--- a/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week01_01Sep.xlsx
+++ b/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week01_01Sep.xlsx
@@ -204,7 +204,7 @@
     <t xml:space="preserve">I can complete a low-pressure science baseline and agree one science target for this half-term.</t>
   </si>
   <si>
-    <t xml:space="preserve">Baseline as a challenge circuit, not a test — matches the English &amp; Maths W1 baselines so pupils meet a consistent, low-threat start.  Soft-start 'what do you already know?' science mind-map → short rotation of low-stakes stations: (1) prior-knowledge probe on cells &amp; the body in student-friendly language; (2) working-scientifically skill check — handle a piece of equipment, read a simple scale, produce a quick labelled drawing; (3) science-literacy &amp; command-word taster (describe / name); (4) science-numeracy taster (read a value, a simple ratio) to flag readiness for the magnification maths in Week 4.  Confidence check → agree ONE science target on a target card.  EVIDENCE: baseline sheet + target card + photo → EFL; this is the starting-point record that Weeks 2+ show progress against.  GCSE NOTE: frames the 1BI0 Foundation journey — where we're heading and why.</t>
+    <t xml:space="preserve">Baseline as a challenge circuit, not a test — matches the English &amp; Maths W1 baselines so pupils meet a consistent, low-threat start.  Soft-start 'what do you already know?' science mind-map → short rotation of low-stakes stations: (1) prior-knowledge probe on cells &amp; the body in student-friendly language; (2) working-scientifically skill check — handle a piece of equipment, read a simple scale, produce a quick labelled drawing; (3) science-literacy &amp; command-word taster (describe / name); (4) science-numeracy taster (read a value, a simple ratio) to flag readiness for the magnification maths in Week 4.  Confidence check → agree ONE science target on a target card.  EVIDENCE: baseline sheet + target card + photo → evidence platform; this is the starting-point record that Weeks 2+ show progress against.  GCSE NOTE: frames the 1BI0 Foundation journey — where we're heading and why.</t>
   </si>
   <si>
     <t xml:space="preserve">baseline, target, cell, label, scale, describe, estimate, working scientifically</t>
@@ -247,7 +247,7 @@
   </si>
   <si>
     <t xml:space="preserve">TA leads a small group and pre-agrees what each pupil is comfortable sharing; quiet space available.
-LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to EFL, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
+LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to evidence platform, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: feeds each pupil's real destination (college/barbering) → PfA plan and IEDP Outcome 5 [NS].</t>
